--- a/Datos-Tratados/SABI.xlsx
+++ b/Datos-Tratados/SABI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodri\Documents\Proyectos\Personal\proyecto-ade-gema\Datos-Tratados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DCAABE-3C06-4B50-86CA-D48E61A67444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E44AC845-D93A-416F-B548-AA954AAD0CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
